--- a/templates/bbc_db_tables_by_sheet.xlsx
+++ b/templates/bbc_db_tables_by_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tshering/Documents/bbccc/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BE3CA2-481D-6140-9DE7-E138150DEFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B416AD-5F7B-4147-8B45-1842E48E4849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" firstSheet="35" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15860" firstSheet="33" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11385" uniqueCount="2228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11391" uniqueCount="2231">
   <si>
     <t>id</t>
   </si>
@@ -6753,13 +6753,22 @@
   </si>
   <si>
     <t>created_by</t>
+  </si>
+  <si>
+    <t>Temp1234!</t>
+  </si>
+  <si>
+    <t>*Testing*8</t>
+  </si>
+  <si>
+    <t>$2y$10$FLiUQjOWgZZUW3ff4h9ATeNKxmZbsbbUhQRCxQ0R7/ilwFkpbelBm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6773,6 +6782,14 @@
       <color rgb="FF1F2A44"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -6812,8 +6829,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -6824,12 +6842,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -23190,10 +23209,12 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
-  <dimension ref="A1:N206"/>
+  <dimension ref="A1:N211"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="14" width="14" customWidth="1"/>
+    <col min="1" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -23378,7 +23399,7 @@
       <c r="C6" t="s">
         <v>518</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F6" t="s">
@@ -27580,7 +27601,7 @@
         <v>1114</v>
       </c>
       <c r="K137">
-        <v>1234</v>
+        <v>2020</v>
       </c>
       <c r="L137" t="s">
         <v>500</v>
@@ -29720,9 +29741,6 @@
       <c r="F204">
         <v>480451551</v>
       </c>
-      <c r="G204" s="4">
-        <v>480451551</v>
-      </c>
       <c r="I204" t="s">
         <v>1396</v>
       </c>
@@ -29752,10 +29770,7 @@
       <c r="E205" t="s">
         <v>1400</v>
       </c>
-      <c r="F205" s="4" t="s">
-        <v>1401</v>
-      </c>
-      <c r="G205" s="4" t="s">
+      <c r="F205" t="s">
         <v>1401</v>
       </c>
       <c r="I205" t="s">
@@ -29787,10 +29802,7 @@
       <c r="E206" t="s">
         <v>1404</v>
       </c>
-      <c r="F206" s="5">
-        <v>451423347</v>
-      </c>
-      <c r="G206" s="4">
+      <c r="F206" s="4">
         <v>451423347</v>
       </c>
       <c r="I206" t="s">
@@ -29809,8 +29821,40 @@
         <v>501</v>
       </c>
     </row>
+    <row r="209" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E209" t="s">
+        <v>1404</v>
+      </c>
+      <c r="F209" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G209" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="210" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E210" s="5" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F210" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="211" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E211" t="s">
+        <v>896</v>
+      </c>
+      <c r="F211" t="s">
+        <v>2229</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E210" r:id="rId1" xr:uid="{115B63DF-7E36-F54E-8E33-46599BB9F61E}"/>
+    <hyperlink ref="E6" r:id="rId2" xr:uid="{9EEE40C2-4731-AA4B-A869-6DF85736B645}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -58498,7 +58542,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="4" max="4" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
     <col min="8" max="9" width="16" customWidth="1"/>
